--- a/upload_excel/NaviTest.xlsx
+++ b/upload_excel/NaviTest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CNXK\Downloads\tagging\unpacktoolgit\upload_excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lyuns\Downloads\unpacktool\unpacktool\upload_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5BD3FD9-144C-4279-A472-D2449A6460CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C4C11B-B329-48E0-AD92-06643958E195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F662C06C-6245-46E3-98E3-CB6C352AD8F1}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{F662C06C-6245-46E3-98E3-CB6C352AD8F1}"/>
   </bookViews>
   <sheets>
     <sheet name="Navi(PDP)" sheetId="2" r:id="rId1"/>
@@ -65,265 +65,267 @@
     <t>SG</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/sg/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>AU</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/au/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>NZ</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/nz/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>ID</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/id/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>TH</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/th/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>MM</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/mm/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>VN</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/vn/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>MY</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/my/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>PH</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/ph/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>JP</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/jp/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>CN</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com.cn/cn/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>HK</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/hk/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>HK_EN</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/hk_en/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>TW</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/tw/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>IN</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/in/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>PK</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/pk/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>BD</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/bd/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>RU</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/ru/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>AZ</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/az/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>UA</t>
   </si>
   <si>
-    <t>https://p6-eu-author.samsung.com/content/samsung/ua/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>KZ_RU</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/kz_ru/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>KZ_KZ</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/kz_kz/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>UZ_RU</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/uz_ru/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>UZ_UZ</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/uz_uz/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>MN</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/mn/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>AE</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/ae/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>AE_AR</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/ae_ar/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>SA_EN</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/sa_en/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>TR</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/tr/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>LEVANT</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/levant/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>LB</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/lb/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>N_AFRICA</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/n_africa/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>AFRICA_EN</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/africa_en/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>AFRICA_FR</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/africa_fr/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>AFRICA_PT</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/africa_pt/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>ZA</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/za/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>IL</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/il/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>PS</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/ps/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>SA</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/sa/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>IRAN</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/iran/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>LEVANT_AR</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/levant_ar/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>IQ_AR</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/iq_ar/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>IQ_KU</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/iq_ku/smartphones/galaxy-s25.html?wcmmode=disabled</t>
-  </si>
-  <si>
     <t>EG</t>
   </si>
   <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/eg/smartphones/galaxy-s25.html?wcmmode=disabled</t>
+    <t>https://www.samsung.comcn/cn/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/au/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/nz/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/id/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/th/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/mm/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/vn/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/my/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/jp/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/hk/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/hk_en/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/tw/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/in/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/pk/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/bd/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/ru/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/az/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://p6-eu-authorsamsungcom/ua/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/kz_ru/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/kz_kz/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/uz_ru/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/uz_uz/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/mn/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/ae/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/ae_ar/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/sa_en/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/tr/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/levant/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/lb/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/n_africa/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/africa_en/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/africa_fr/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/africa_pt/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/za/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/il/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/ps/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/sa/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/iran/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/levant_ar/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/iq_ar/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/iq_ku/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/eg/smartphones/galaxy-s25</t>
+  </si>
+  <si>
+    <t>https://www.samsung.com/ph/smartphones/galaxy-s25</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.samsung.com/sg/smartphones/galaxy-s25</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -902,17 +904,17 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A2:G48"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="14.4" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.09765625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.69921875" style="8" customWidth="1"/>
-    <col min="3" max="3" width="105.59765625" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.3984375" style="8" customWidth="1"/>
-    <col min="5" max="5" width="13.69921875" style="8" customWidth="1"/>
+    <col min="1" max="1" width="1.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.75" style="8" customWidth="1"/>
+    <col min="3" max="3" width="105.625" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="13.75" style="8" customWidth="1"/>
     <col min="6" max="16384" width="8" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" ht="25.8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="26.25" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
@@ -920,14 +922,14 @@
       <c r="D2" s="2"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" s="6" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="5"/>
       <c r="C3" s="17"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
     </row>
-    <row r="4" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
       <c r="B4" s="9" t="s">
         <v>0</v>
       </c>
@@ -941,420 +943,420 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>6</v>
+        <v>92</v>
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="13"/>
     </row>
-    <row r="6" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B6" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="D6" s="14"/>
       <c r="E6" s="15"/>
     </row>
-    <row r="7" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B7" s="11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="15"/>
     </row>
-    <row r="8" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B8" s="11" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="15"/>
     </row>
-    <row r="9" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B9" s="11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="15"/>
     </row>
-    <row r="10" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B10" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="D10" s="14"/>
       <c r="E10" s="15"/>
     </row>
-    <row r="11" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B11" s="11" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="D11" s="14"/>
       <c r="E11" s="15"/>
     </row>
-    <row r="12" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B12" s="11" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="15"/>
     </row>
-    <row r="13" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B13" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>22</v>
+        <v>13</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>91</v>
       </c>
       <c r="D13" s="14"/>
       <c r="E13" s="15"/>
       <c r="G13" s="7"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B14" s="16" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="D14" s="16"/>
       <c r="E14" s="16"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B15" s="16" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="D15" s="16"/>
       <c r="E15" s="16"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B16" s="16" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="D16" s="16"/>
       <c r="E16" s="16"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="16" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="D17" s="16"/>
       <c r="E17" s="16"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="16" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="16" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="16" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="16" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="16" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="16" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="D23" s="16"/>
       <c r="E23" s="16"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="16" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="D24" s="16"/>
       <c r="E24" s="16"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="D25" s="16"/>
       <c r="E25" s="16"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="16" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="D26" s="16"/>
       <c r="E26" s="16"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" s="16" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" s="16" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" s="16" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="D29" s="16"/>
       <c r="E29" s="16"/>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30" s="16" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="D30" s="16"/>
       <c r="E30" s="16"/>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" s="16" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32" s="16" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="D32" s="16"/>
       <c r="E32" s="16"/>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33" s="16" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="D33" s="16"/>
       <c r="E33" s="16"/>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34" s="16" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="D34" s="16"/>
       <c r="E34" s="16"/>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35" s="16" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D35" s="16"/>
       <c r="E35" s="16"/>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36" s="16" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D36" s="16"/>
       <c r="E36" s="16"/>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37" s="16" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D37" s="16"/>
       <c r="E37" s="16"/>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B38" s="16" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B39" s="16" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="D39" s="16"/>
       <c r="E39" s="16"/>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B40" s="16" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D40" s="16"/>
       <c r="E40" s="16"/>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B41" s="16" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D41" s="16"/>
       <c r="E41" s="16"/>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B42" s="16" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D42" s="16"/>
       <c r="E42" s="16"/>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B43" s="16" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D43" s="16"/>
       <c r="E43" s="16"/>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B44" s="16" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D44" s="16"/>
       <c r="E44" s="16"/>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B45" s="16" t="s">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D45" s="16"/>
       <c r="E45" s="16"/>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B46" s="16" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="C46" s="19" t="s">
         <v>88</v>
@@ -1362,37 +1364,42 @@
       <c r="D46" s="16"/>
       <c r="E46" s="16"/>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B47" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C47" s="19" t="s">
         <v>89</v>
-      </c>
-      <c r="C47" s="19" t="s">
-        <v>90</v>
       </c>
       <c r="D47" s="16"/>
       <c r="E47" s="16"/>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B48" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="C48" s="19" t="s">
-        <v>92</v>
+        <v>48</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>90</v>
       </c>
       <c r="D48" s="16"/>
       <c r="E48" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C48" r:id="rId1" display="https://wwwsamsungcom/content/samsung/eg/smartphones/galaxy-s25" xr:uid="{30D46E2A-7551-4F44-90EC-9E0868E0A8D0}"/>
+    <hyperlink ref="C13" r:id="rId2" xr:uid="{5CE44865-7651-4FAF-8382-0C306A26C7B5}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{B4B7FF83-EEA1-4039-A893-7BAAD3BB5BBC}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EB3B907-CD05-4796-898C-059E3C00B187}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
